--- a/resultados/tresbarrasdoparana/inventario_externos.xlsx
+++ b/resultados/tresbarrasdoparana/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3614,6 +3614,41 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://servicos.tce.pr.gov.br/servicos/srv_consultaprocesso.aspx?processoMaster=16067821&amp;page=cpc</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>servicos.tce.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://servicos.tce.pr.gov.br/servicos/srv_consultaprocesso.aspx?processoMaster=16067821&amp;page=cpc</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/orcamento/pca/pca-exercicio-2020</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>3</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:38:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/tresbarrasdoparana/inventario_externos.xlsx
+++ b/resultados/tresbarrasdoparana/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3649,6 +3649,286 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://institutounicampo.com.br/concurso/processo-seletivo-simplificado-pss-prefeitura-municipal-de-tres-barras-do-parana-pr_</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>institutounicampo.com.br</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://institutounicampo.com.br/concurso/processo-seletivo-simplificado-pss-prefeitura-municipal-de-tres-barras-do-parana-pr_</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/adm/concursos/processo-seletivo-simplificado-n-001-2025</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>3</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-08-07 15:49:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSd6yCJ1F35SZEAi5GSQTFa_-oJTs9eEtJoQzBO6smkOaDTUNQ/viewform?usp=pp_url</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Inscreva-se aqui</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/adm/concursos/processo-seletivo-simplificado-professor-n-001-2023</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-08-07 15:52:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSc5aw8v08TygX99RzPbVeNhm-XsWFZ-xFNoA9P2yT3cshKEQw/viewform?usp=pp_url</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Formulário de recurso</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/adm/concursos/processo-seletivo-simplificado-professor-n-001-2023</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>3</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-08-07 15:52:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://ippec.org.br/concursos/concurso/144</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ippec.org.br</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://ippec.org.br/concursos/concurso/144</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/adm/concursos/processo-seletivo-simplificado-n-001-2022</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>3</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:03:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://ippec.org.br/concursos/concurso/114</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ippec.org.br</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://ippec.org.br/concursos/concurso/114</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/adm/concursos/processo-seletivo-simplificado-n-003-2021</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>3</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:05:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://concursos.alfaumuarama.edu.br/concursos/concurso/116</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>concursos.alfaumuarama.edu.br</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://concursos.alfaumuarama.edu.br/concursos/concurso/116</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/adm/concursos/processo-seletivo-simplificado-n-002-2021</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>3</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:06:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSfguQHV_vrla2HaZMEupXJZUgG8CFpDrxAVhzxrBw-nWbtZgA/viewform</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSfguQHV_vrla2HaZMEupXJZUgG8CFpDrxAVhzxrBw-nWbtZgA/viewform</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/adm/concursos/teste-seletivo-n-001-2021</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:07:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSfg3GZNXpjlOf4nCCn3KE76bZTum9yw46QMChMLaUkq5KXoZQ/viewform</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSfg3GZNXpjlOf4nCCn3KE76bZTum9yw46QMChMLaUkq5KXoZQ/viewform</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/adm/concursos/processo-seletivo-simplificado-pss-da-secretaria-municipal-de-saude-2</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>3</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:09:06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/tresbarrasdoparana/inventario_externos.xlsx
+++ b/resultados/tresbarrasdoparana/inventario_externos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3929,6 +3929,76 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>http://www.bll.org.br</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>www.bll.org.br</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>www.bll.org.br</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/adm/licitacoes/tomada-de-precos/tomada-de-precos-n-06-2023-contratacao-de-empresa-para-execucao-de-pavimentacao-poliedrica-nas-ruas-pavao-jau-ijui-timbo-e-prolongamento-da-rua-mato-grosso-conforme-contrato-de-repasse-n-939636-2022-mdr-caixa</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>3</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:18:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.trêsbarras.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>www.trêsbarras.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>www.trêsbarras.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/adm/licitacoes/chamamento-publico/chamamento-publico-02-2021-credenciamento-de-pessoa-juridica-para-prestacao-de-servicos-medicos-de-urgencia-e-emergencia-na-forma-de-plantoes-medicos-de-12-horas-para-atender-as-demandas-dos-pacientes-no-hospital-municipal-de-tres-barras-do-parana-abrangendo-os-servicos-descritos-no-termo-de-referencia-anexo-ix-do-edital</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>3</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:24:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/tresbarrasdoparana/inventario_externos.xlsx
+++ b/resultados/tresbarrasdoparana/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3999,6 +3999,1086 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>http://webapp1-tresbarras.cidade360.cloud/pronimtb/index.asp?acao=4&amp;item=4</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>webapp1-tresbarras.cidade360.cloud</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Servidores inativos</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>5</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>http://webapp1-tresbarras.cidade360.cloud/pronimtb/index.asp?acao=4&amp;item=3</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>webapp1-tresbarras.cidade360.cloud</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Cedidos a outros órgãos</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>5</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>http://webapp1-tresbarras.cidade360.cloud/pronimtb/index.asp?acao=4&amp;item=5</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>webapp1-tresbarras.cidade360.cloud</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Quadro funcional</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>5</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>http://webapp1-tresbarras.cidade360.cloud/pronimtb/index.asp?acao=3&amp;item=10</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>webapp1-tresbarras.cidade360.cloud</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Credores</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>http://webapp1-tresbarras.cidade360.cloud/pronimtb/index.asp?acao=1&amp;item=4</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>webapp1-tresbarras.cidade360.cloud</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Produtos</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>http://tresbarras.govbr.cloud/pronimtb/index.asp?acao=4&amp;item=5</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>tresbarras.govbr.cloud</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Quadro Funcional</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>5</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>http://tresbarras.govbr.cloud/pronimtb/index.asp?acao=4&amp;item=3</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>tresbarras.govbr.cloud</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Servidores Inativos</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>5</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>http://tresbarras.govbr.cloud/pronimtb/index.asp?acao=3&amp;item=15</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>tresbarras.govbr.cloud</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Diárias/Passagens (PronimTB)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>5</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>http://tresbarras.govbr.cloud/pronimtb/index.asp?acao=2&amp;item=1</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>tresbarras.govbr.cloud</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Receitas arrecadadas</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>http://tresbarras.govbr.cloud/pronimtb/index.asp?acao=3&amp;item=8</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>tresbarras.govbr.cloud</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>por Natureza da Receita</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>5</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>http://tresbarras.govbr.cloud/pronimtb/index.asp?acao=3&amp;item=9</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>tresbarras.govbr.cloud</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>por Fonte de Recursos</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>5</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>http://tresbarras.govbr.cloud/pronimtb/index.asp?acao=3&amp;item=12</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>tresbarras.govbr.cloud</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Receitas diárias</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>5</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>http://tresbarras.govbr.cloud/pronimtb/index.asp?acao=3&amp;item=4</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>tresbarras.govbr.cloud</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>por Classificação Institucional</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/transparencia</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>5</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/servico/abertura-ouvidoria/executar.html</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>tresbarras.cidade360.cloud</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Faça sua solicitação</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>http://www.tresbarras.pr.gov.br/ouvidoria</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>5</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>http://www.escolacapitulo1.com.br/</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>www.escolacapitulo1.com.br</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/atos/leis/lei-complementar-n-001-2014</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>5</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-08-15 13:10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:32:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:32:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://www.telegram.com/</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>www.telegram.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:32:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.whatsapp.com/</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>www.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:32:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://www.x.com/</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>www.x.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:32:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://www.governancabrasil.com.br/</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>www.governancabrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:32:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://www.volarisgroup.com/pt-br</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>www.volarisgroup.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Volaris Group</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:32:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/governodigital/pt-br/acessibilidade-digital/eMAGv31.pdf</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>www.gov.br</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Modelo de Acessibilidade em Governo Eletrônico - eMAG</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:23:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://www.w3.org/TR/WCAG21/</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>www.w3.org</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Web Content Accessibility Guidelines (em inglês)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:23:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://vlibras.gov.br/</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>vlibras.gov.br</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VLibras</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:23:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://www.nvaccess.org/download/</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>www.nvaccess.org</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NVDA (em inglês)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:23:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://support.freedomscientific.com/Downloads/JAWS</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>support.freedomscientific.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>JAWS (em inglês)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:23:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://support.apple.com/pt-br/guide/voiceover/welcome/mac</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>support.apple.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>VoiceOver</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:23:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:23:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/sharer.php?u=</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:23:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://twitter.com/share?text=</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:23:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://tresbarras.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:23:56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
